--- a/연구코드/results/regression/gangnam/male/regression_results.xlsx
+++ b/연구코드/results/regression/gangnam/male/regression_results.xlsx
@@ -557,13 +557,13 @@
         <v>0.0441</v>
       </c>
       <c r="M2">
-        <v>0.7557</v>
+        <v>0.729</v>
       </c>
       <c r="N2">
-        <v>0.2258</v>
+        <v>0.8511</v>
       </c>
       <c r="O2">
-        <v>0.9267</v>
+        <v>0.6895</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -604,13 +604,13 @@
         <v>0.0329</v>
       </c>
       <c r="M3">
-        <v>0.7805</v>
+        <v>0.7195</v>
       </c>
       <c r="N3">
-        <v>0.3037</v>
+        <v>0.8671</v>
       </c>
       <c r="O3">
-        <v>0.9343</v>
+        <v>0.6719000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -651,13 +651,13 @@
         <v>0.0367</v>
       </c>
       <c r="M4">
-        <v>0.7729</v>
+        <v>0.7042</v>
       </c>
       <c r="N4">
-        <v>0.2963</v>
+        <v>0.8982</v>
       </c>
       <c r="O4">
-        <v>0.9267</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -698,13 +698,13 @@
         <v>0.0142</v>
       </c>
       <c r="M5">
-        <v>0.7766</v>
+        <v>0.727</v>
       </c>
       <c r="N5">
-        <v>0.3671</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="O5">
-        <v>0.9091</v>
+        <v>0.6843</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -745,13 +745,13 @@
         <v>0.0217</v>
       </c>
       <c r="M6">
-        <v>0.7768</v>
+        <v>0.7194</v>
       </c>
       <c r="N6">
-        <v>0.3748</v>
+        <v>0.8748</v>
       </c>
       <c r="O6">
-        <v>0.9066</v>
+        <v>0.6693</v>
       </c>
     </row>
   </sheetData>
